--- a/Cronograma/Itinerario-Garcia_Eduardo VNª0.1.xlsx
+++ b/Cronograma/Itinerario-Garcia_Eduardo VNª0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e4c1149bfe4a44f7/Desktop/10101_PPP/10109_PPP/Cronograma/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{36C23E7B-EB67-469A-B510-ECB4390D68D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{36C23E7B-EB67-469A-B510-ECB4390D68D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C34798D-1F4C-430B-ABA7-5C9A4AAC817E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActividadesDetalle" sheetId="5" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
   <si>
     <t>FECHA</t>
   </si>
@@ -183,6 +183,15 @@
   </si>
   <si>
     <t>Desarrollo backend para funcionalidad de preguntas frecuentes</t>
+  </si>
+  <si>
+    <t>8:30 am - 15:30 pm</t>
+  </si>
+  <si>
+    <t>Tecnología y Desarrollo</t>
+  </si>
+  <si>
+    <t>Automatización y desarrollo de software</t>
   </si>
 </sst>
 </file>
@@ -408,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -505,71 +514,74 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -851,65 +863,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J220"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.25" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
-    <col min="2" max="2" width="55.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="55.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="19.375" customWidth="1"/>
+    <col min="2" max="2" width="55.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="55.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.75" style="4" customWidth="1"/>
+    <col min="6" max="6" width="14.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1"/>
+    <col min="8" max="8" width="10.125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
-      <c r="B1" s="50" t="s">
+    <row r="1" spans="1:8" ht="24.75" x14ac:dyDescent="0.5">
+      <c r="B1" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-    </row>
-    <row r="2" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="54">
+      <c r="B2" s="36">
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="54">
+      <c r="B3" s="36">
         <v>46142</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="58" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="58" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:8" ht="52.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="58" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="8" spans="1:8" ht="52.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>0</v>
       </c>
@@ -933,11 +951,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="47">
+    <row r="9" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="49">
         <v>46082</v>
       </c>
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="49" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="18" t="s">
@@ -947,17 +965,17 @@
         <v>2</v>
       </c>
       <c r="E9" s="18"/>
-      <c r="F9" s="43" t="s">
+      <c r="F9" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="39">
+      <c r="G9" s="41">
         <v>6</v>
       </c>
-      <c r="H9" s="53"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="48"/>
-      <c r="B10" s="48"/>
+      <c r="H9" s="55"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="54"/>
+      <c r="B10" s="54"/>
       <c r="C10" s="18" t="s">
         <v>18</v>
       </c>
@@ -967,13 +985,13 @@
       <c r="E10" s="18">
         <v>6</v>
       </c>
-      <c r="F10" s="44"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="55"/>
-    </row>
-    <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="49"/>
-      <c r="B11" s="49"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="56"/>
+    </row>
+    <row r="11" spans="1:8" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="50"/>
+      <c r="B11" s="50"/>
       <c r="C11" s="18" t="s">
         <v>19</v>
       </c>
@@ -981,15 +999,15 @@
         <v>2</v>
       </c>
       <c r="E11" s="18"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="55"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="42">
+      <c r="F11" s="40"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="56"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="48">
         <v>46083</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="47" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="18" t="s">
@@ -999,17 +1017,17 @@
         <v>2</v>
       </c>
       <c r="E12" s="18"/>
-      <c r="F12" s="37" t="s">
+      <c r="F12" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="38">
+      <c r="G12" s="47">
         <v>6</v>
       </c>
-      <c r="H12" s="55"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="42"/>
-      <c r="B13" s="38"/>
+      <c r="H12" s="56"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="48"/>
+      <c r="B13" s="47"/>
       <c r="C13" s="18" t="s">
         <v>21</v>
       </c>
@@ -1017,13 +1035,13 @@
         <v>2</v>
       </c>
       <c r="E13" s="18"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="55"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="42"/>
-      <c r="B14" s="38"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="56"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="48"/>
+      <c r="B14" s="47"/>
       <c r="C14" s="18" t="s">
         <v>22</v>
       </c>
@@ -1033,13 +1051,13 @@
       <c r="E14" s="18">
         <v>6</v>
       </c>
-      <c r="F14" s="37"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="55"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="42"/>
-      <c r="B15" s="38"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="56"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="48"/>
+      <c r="B15" s="47"/>
       <c r="C15" s="18" t="s">
         <v>23</v>
       </c>
@@ -1047,15 +1065,15 @@
         <v>1</v>
       </c>
       <c r="E15" s="18"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="55"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="42">
+      <c r="F15" s="44"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="56"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="48">
         <v>46084</v>
       </c>
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="48" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="18" t="s">
@@ -1065,17 +1083,17 @@
         <v>2</v>
       </c>
       <c r="E16" s="18"/>
-      <c r="F16" s="37" t="s">
+      <c r="F16" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="38">
+      <c r="G16" s="47">
         <v>6</v>
       </c>
-      <c r="H16" s="55"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="42"/>
-      <c r="B17" s="42"/>
+      <c r="H16" s="56"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="48"/>
+      <c r="B17" s="48"/>
       <c r="C17" s="18" t="s">
         <v>27</v>
       </c>
@@ -1085,13 +1103,13 @@
       <c r="E17" s="18">
         <v>6</v>
       </c>
-      <c r="F17" s="37"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="55"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="42"/>
-      <c r="B18" s="42"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="56"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
       <c r="C18" s="18" t="s">
         <v>28</v>
       </c>
@@ -1099,15 +1117,15 @@
         <v>2</v>
       </c>
       <c r="E18" s="18"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="55"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="42">
+      <c r="F18" s="44"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="56"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="48">
         <v>46085</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="48" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="18" t="s">
@@ -1117,17 +1135,17 @@
         <v>2</v>
       </c>
       <c r="E19" s="18"/>
-      <c r="F19" s="37" t="s">
+      <c r="F19" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="38">
+      <c r="G19" s="47">
         <v>6</v>
       </c>
-      <c r="H19" s="55"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="42"/>
-      <c r="B20" s="42"/>
+      <c r="H19" s="56"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="48"/>
+      <c r="B20" s="48"/>
       <c r="C20" s="18" t="s">
         <v>31</v>
       </c>
@@ -1137,13 +1155,13 @@
       <c r="E20" s="18">
         <v>6</v>
       </c>
-      <c r="F20" s="37"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="55"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="42"/>
-      <c r="B21" s="42"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="56"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
       <c r="C21" s="18" t="s">
         <v>32</v>
       </c>
@@ -1151,51 +1169,51 @@
         <v>2</v>
       </c>
       <c r="E21" s="18"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="55"/>
-    </row>
-    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="42">
+      <c r="F21" s="44"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="56"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" s="48">
         <v>46086</v>
       </c>
-      <c r="B22" s="42" t="s">
+      <c r="B22" s="48" t="s">
         <v>37</v>
       </c>
       <c r="C22" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="57">
+      <c r="D22" s="37">
         <v>2</v>
       </c>
       <c r="E22" s="18"/>
-      <c r="F22" s="43" t="s">
+      <c r="F22" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="39">
+      <c r="G22" s="41">
         <v>6</v>
       </c>
-      <c r="H22" s="55"/>
-    </row>
-    <row r="23" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="42"/>
-      <c r="B23" s="42"/>
+      <c r="H22" s="56"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A23" s="48"/>
+      <c r="B23" s="48"/>
       <c r="C23" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="57">
+      <c r="D23" s="37">
         <v>1</v>
       </c>
       <c r="E23" s="18">
         <v>6</v>
       </c>
-      <c r="F23" s="44"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="55"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="42"/>
-      <c r="B24" s="42"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="56"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A24" s="48"/>
+      <c r="B24" s="48"/>
       <c r="C24" s="18" t="s">
         <v>35</v>
       </c>
@@ -1203,13 +1221,13 @@
         <v>1</v>
       </c>
       <c r="E24" s="18"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="55"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="42"/>
-      <c r="B25" s="42"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="56"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A25" s="48"/>
+      <c r="B25" s="48"/>
       <c r="C25" s="18" t="s">
         <v>36</v>
       </c>
@@ -1217,15 +1235,15 @@
         <v>2</v>
       </c>
       <c r="E25" s="18"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="55"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="42">
+      <c r="F25" s="40"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="56"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A26" s="48">
         <v>46089</v>
       </c>
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="48" t="s">
         <v>38</v>
       </c>
       <c r="C26" s="20" t="s">
@@ -1235,17 +1253,17 @@
         <v>1</v>
       </c>
       <c r="E26" s="18"/>
-      <c r="F26" s="43" t="s">
+      <c r="F26" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="G26" s="39">
+      <c r="G26" s="41">
         <v>6</v>
       </c>
-      <c r="H26" s="55"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="42"/>
-      <c r="B27" s="42"/>
+      <c r="H26" s="56"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
       <c r="C27" s="18" t="s">
         <v>40</v>
       </c>
@@ -1255,13 +1273,13 @@
       <c r="E27" s="18">
         <v>6</v>
       </c>
-      <c r="F27" s="44"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="55"/>
-    </row>
-    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="42"/>
-      <c r="B28" s="42"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="56"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A28" s="48"/>
+      <c r="B28" s="48"/>
       <c r="C28" s="18" t="s">
         <v>41</v>
       </c>
@@ -1269,13 +1287,13 @@
         <v>2</v>
       </c>
       <c r="E28" s="18"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="55"/>
-    </row>
-    <row r="29" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="42"/>
-      <c r="B29" s="42"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="56"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A29" s="48"/>
+      <c r="B29" s="48"/>
       <c r="C29" s="18" t="s">
         <v>42</v>
       </c>
@@ -1283,1491 +1301,1491 @@
         <v>2</v>
       </c>
       <c r="E29" s="18"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="55"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="42"/>
-      <c r="B30" s="42"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="56"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
       <c r="C30" s="18"/>
       <c r="D30" s="19"/>
       <c r="E30" s="18"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="39"/>
-      <c r="H30" s="55"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="42"/>
-      <c r="B31" s="42"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="56"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
       <c r="C31" s="18"/>
       <c r="D31" s="19"/>
       <c r="E31" s="18"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="55"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="42"/>
-      <c r="B32" s="42"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="56"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A32" s="48"/>
+      <c r="B32" s="48"/>
       <c r="C32" s="18"/>
       <c r="D32" s="19"/>
       <c r="E32" s="18"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="55"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="42"/>
-      <c r="B33" s="42"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="56"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A33" s="48"/>
+      <c r="B33" s="48"/>
       <c r="C33" s="22"/>
       <c r="D33" s="19"/>
       <c r="E33" s="18"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="55"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="42"/>
-      <c r="B34" s="42"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="56"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A34" s="48"/>
+      <c r="B34" s="48"/>
       <c r="C34" s="18"/>
       <c r="D34" s="19"/>
       <c r="E34" s="18"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="55"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="42"/>
-      <c r="B35" s="42"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="56"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" s="48"/>
+      <c r="B35" s="48"/>
       <c r="C35" s="18"/>
       <c r="D35" s="19"/>
       <c r="E35" s="18"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="55"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="42"/>
-      <c r="B36" s="42"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="56"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A36" s="48"/>
+      <c r="B36" s="48"/>
       <c r="C36" s="18"/>
       <c r="D36" s="19"/>
       <c r="E36" s="18"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="55"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="42"/>
-      <c r="B37" s="42"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="56"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A37" s="48"/>
+      <c r="B37" s="48"/>
       <c r="C37" s="18"/>
       <c r="D37" s="19"/>
       <c r="E37" s="18"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="39"/>
-      <c r="H37" s="55"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="42"/>
-      <c r="B38" s="42"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="56"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A38" s="48"/>
+      <c r="B38" s="48"/>
       <c r="C38" s="18"/>
       <c r="D38" s="19"/>
       <c r="E38" s="18"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="55"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="42"/>
-      <c r="B39" s="42"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="56"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A39" s="48"/>
+      <c r="B39" s="48"/>
       <c r="C39" s="18"/>
       <c r="D39" s="19"/>
       <c r="E39" s="18"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="55"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="42"/>
-      <c r="B40" s="42"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="46"/>
+      <c r="H39" s="56"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A40" s="48"/>
+      <c r="B40" s="48"/>
       <c r="C40" s="18"/>
       <c r="D40" s="19"/>
       <c r="E40" s="18"/>
-      <c r="F40" s="45"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="55"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="42"/>
-      <c r="B41" s="38"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="56"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A41" s="48"/>
+      <c r="B41" s="47"/>
       <c r="C41" s="22"/>
       <c r="D41" s="19"/>
       <c r="E41" s="18"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="55"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="42"/>
-      <c r="B42" s="38"/>
+      <c r="F41" s="44"/>
+      <c r="G41" s="47"/>
+      <c r="H41" s="56"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A42" s="48"/>
+      <c r="B42" s="47"/>
       <c r="C42" s="18"/>
       <c r="D42" s="19"/>
       <c r="E42" s="18"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="55"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="42"/>
-      <c r="B43" s="38"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="56"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A43" s="48"/>
+      <c r="B43" s="47"/>
       <c r="C43" s="18"/>
       <c r="D43" s="19"/>
       <c r="E43" s="18"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="55"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="42"/>
-      <c r="B44" s="38"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="47"/>
+      <c r="H43" s="56"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A44" s="48"/>
+      <c r="B44" s="47"/>
       <c r="C44" s="18"/>
       <c r="D44" s="19"/>
       <c r="E44" s="18"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="55"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="42"/>
-      <c r="B45" s="42"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="56"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A45" s="48"/>
+      <c r="B45" s="48"/>
       <c r="C45" s="19"/>
       <c r="D45" s="19"/>
       <c r="E45" s="18"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="39"/>
-      <c r="H45" s="55"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="42"/>
-      <c r="B46" s="42"/>
+      <c r="F45" s="39"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="56"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A46" s="48"/>
+      <c r="B46" s="48"/>
       <c r="C46" s="19"/>
       <c r="D46" s="19"/>
       <c r="E46" s="18"/>
-      <c r="F46" s="44"/>
-      <c r="G46" s="40"/>
-      <c r="H46" s="55"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="42"/>
-      <c r="B47" s="42"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="56"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A47" s="48"/>
+      <c r="B47" s="48"/>
       <c r="C47" s="19"/>
       <c r="D47" s="19"/>
       <c r="E47" s="18"/>
-      <c r="F47" s="45"/>
-      <c r="G47" s="41"/>
-      <c r="H47" s="55"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="42"/>
-      <c r="B48" s="42"/>
+      <c r="F47" s="40"/>
+      <c r="G47" s="42"/>
+      <c r="H47" s="56"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48" s="48"/>
+      <c r="B48" s="48"/>
       <c r="C48" s="19"/>
       <c r="D48" s="19"/>
       <c r="E48" s="18"/>
-      <c r="F48" s="43"/>
-      <c r="G48" s="39"/>
-      <c r="H48" s="55"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="42"/>
-      <c r="B49" s="42"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="56"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A49" s="48"/>
+      <c r="B49" s="48"/>
       <c r="C49" s="19"/>
       <c r="D49" s="19"/>
       <c r="E49" s="18"/>
-      <c r="F49" s="44"/>
-      <c r="G49" s="40"/>
-      <c r="H49" s="55"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="42"/>
-      <c r="B50" s="42"/>
+      <c r="F49" s="45"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="56"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A50" s="48"/>
+      <c r="B50" s="48"/>
       <c r="C50" s="19"/>
       <c r="D50" s="19"/>
       <c r="E50" s="18"/>
-      <c r="F50" s="45"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="55"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="56"/>
       <c r="J50" s="12"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="42"/>
-      <c r="B51" s="47"/>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A51" s="48"/>
+      <c r="B51" s="49"/>
       <c r="C51" s="19"/>
       <c r="D51" s="19"/>
       <c r="E51" s="18"/>
-      <c r="F51" s="43"/>
-      <c r="G51" s="39"/>
-      <c r="H51" s="55"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="42"/>
-      <c r="B52" s="48"/>
+      <c r="F51" s="39"/>
+      <c r="G51" s="41"/>
+      <c r="H51" s="56"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A52" s="48"/>
+      <c r="B52" s="54"/>
       <c r="C52" s="19"/>
       <c r="D52" s="19"/>
       <c r="E52" s="18"/>
-      <c r="F52" s="44"/>
-      <c r="G52" s="40"/>
-      <c r="H52" s="55"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="42"/>
-      <c r="B53" s="49"/>
+      <c r="F52" s="45"/>
+      <c r="G52" s="46"/>
+      <c r="H52" s="56"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A53" s="48"/>
+      <c r="B53" s="50"/>
       <c r="C53" s="19"/>
       <c r="D53" s="19"/>
       <c r="E53" s="18"/>
-      <c r="F53" s="45"/>
-      <c r="G53" s="41"/>
-      <c r="H53" s="55"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="42"/>
+      <c r="H53" s="56"/>
       <c r="J53" s="12"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="42"/>
-      <c r="B54" s="42"/>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A54" s="48"/>
+      <c r="B54" s="48"/>
       <c r="C54" s="19"/>
       <c r="D54" s="19"/>
       <c r="E54" s="18"/>
-      <c r="F54" s="43"/>
-      <c r="G54" s="39"/>
-      <c r="H54" s="55"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="42"/>
-      <c r="B55" s="42"/>
+      <c r="F54" s="39"/>
+      <c r="G54" s="41"/>
+      <c r="H54" s="56"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A55" s="48"/>
+      <c r="B55" s="48"/>
       <c r="C55" s="19"/>
       <c r="D55" s="19"/>
       <c r="E55" s="18"/>
-      <c r="F55" s="44"/>
-      <c r="G55" s="40"/>
-      <c r="H55" s="55"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="42"/>
-      <c r="B56" s="42"/>
+      <c r="F55" s="45"/>
+      <c r="G55" s="46"/>
+      <c r="H55" s="56"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A56" s="48"/>
+      <c r="B56" s="48"/>
       <c r="C56" s="19"/>
       <c r="D56" s="19"/>
       <c r="E56" s="18"/>
-      <c r="F56" s="45"/>
-      <c r="G56" s="41"/>
-      <c r="H56" s="55"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="42"/>
-      <c r="B57" s="42"/>
+      <c r="F56" s="40"/>
+      <c r="G56" s="42"/>
+      <c r="H56" s="56"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A57" s="48"/>
+      <c r="B57" s="48"/>
       <c r="C57" s="19"/>
       <c r="D57" s="19"/>
       <c r="E57" s="18"/>
-      <c r="F57" s="43"/>
-      <c r="G57" s="39"/>
-      <c r="H57" s="55"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="42"/>
-      <c r="B58" s="42"/>
+      <c r="F57" s="39"/>
+      <c r="G57" s="41"/>
+      <c r="H57" s="56"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A58" s="48"/>
+      <c r="B58" s="48"/>
       <c r="C58" s="19"/>
       <c r="D58" s="19"/>
       <c r="E58" s="18"/>
-      <c r="F58" s="44"/>
-      <c r="G58" s="40"/>
-      <c r="H58" s="55"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="42"/>
-      <c r="B59" s="42"/>
+      <c r="F58" s="45"/>
+      <c r="G58" s="46"/>
+      <c r="H58" s="56"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A59" s="48"/>
+      <c r="B59" s="48"/>
       <c r="C59" s="19"/>
       <c r="D59" s="19"/>
       <c r="E59" s="18"/>
-      <c r="F59" s="45"/>
-      <c r="G59" s="41"/>
-      <c r="H59" s="55"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="42"/>
-      <c r="B60" s="42"/>
+      <c r="F59" s="40"/>
+      <c r="G59" s="42"/>
+      <c r="H59" s="56"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A60" s="48"/>
+      <c r="B60" s="48"/>
       <c r="C60" s="19"/>
       <c r="D60" s="19"/>
       <c r="E60" s="18"/>
-      <c r="F60" s="43"/>
-      <c r="G60" s="39"/>
-      <c r="H60" s="55"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="42"/>
-      <c r="B61" s="42"/>
+      <c r="F60" s="39"/>
+      <c r="G60" s="41"/>
+      <c r="H60" s="56"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A61" s="48"/>
+      <c r="B61" s="48"/>
       <c r="C61" s="19"/>
       <c r="D61" s="19"/>
       <c r="E61" s="18"/>
-      <c r="F61" s="44"/>
-      <c r="G61" s="40"/>
-      <c r="H61" s="55"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="42"/>
-      <c r="B62" s="42"/>
+      <c r="F61" s="45"/>
+      <c r="G61" s="46"/>
+      <c r="H61" s="56"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A62" s="48"/>
+      <c r="B62" s="48"/>
       <c r="C62" s="19"/>
       <c r="D62" s="21"/>
       <c r="E62" s="18"/>
-      <c r="F62" s="44"/>
-      <c r="G62" s="40"/>
-      <c r="H62" s="55"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="42"/>
-      <c r="B63" s="42"/>
+      <c r="F62" s="45"/>
+      <c r="G62" s="46"/>
+      <c r="H62" s="56"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A63" s="48"/>
+      <c r="B63" s="48"/>
       <c r="C63" s="19"/>
       <c r="D63" s="21"/>
       <c r="E63" s="18"/>
-      <c r="F63" s="45"/>
-      <c r="G63" s="41"/>
-      <c r="H63" s="55"/>
+      <c r="F63" s="40"/>
+      <c r="G63" s="42"/>
+      <c r="H63" s="56"/>
       <c r="J63" s="12"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="42"/>
-      <c r="B64" s="42"/>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A64" s="48"/>
+      <c r="B64" s="48"/>
       <c r="C64" s="19"/>
       <c r="D64" s="19"/>
       <c r="E64" s="17"/>
-      <c r="F64" s="43"/>
-      <c r="G64" s="39"/>
-      <c r="H64" s="55"/>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="42"/>
-      <c r="B65" s="42"/>
+      <c r="F64" s="39"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="56"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A65" s="48"/>
+      <c r="B65" s="48"/>
       <c r="C65" s="19"/>
       <c r="D65" s="19"/>
       <c r="E65" s="17"/>
-      <c r="F65" s="44"/>
-      <c r="G65" s="40"/>
-      <c r="H65" s="55"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="42"/>
-      <c r="B66" s="42"/>
+      <c r="F65" s="45"/>
+      <c r="G65" s="46"/>
+      <c r="H65" s="56"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A66" s="48"/>
+      <c r="B66" s="48"/>
       <c r="C66" s="19"/>
       <c r="D66" s="19"/>
       <c r="E66" s="17"/>
-      <c r="F66" s="44"/>
-      <c r="G66" s="40"/>
-      <c r="H66" s="55"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="42"/>
-      <c r="B67" s="42"/>
+      <c r="F66" s="45"/>
+      <c r="G66" s="46"/>
+      <c r="H66" s="56"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A67" s="48"/>
+      <c r="B67" s="48"/>
       <c r="C67" s="19"/>
       <c r="D67" s="19"/>
       <c r="E67" s="18"/>
-      <c r="F67" s="45"/>
-      <c r="G67" s="41"/>
-      <c r="H67" s="55"/>
+      <c r="F67" s="40"/>
+      <c r="G67" s="42"/>
+      <c r="H67" s="56"/>
       <c r="J67" s="12"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="42"/>
-      <c r="B68" s="42"/>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A68" s="48"/>
+      <c r="B68" s="48"/>
       <c r="C68" s="19"/>
       <c r="D68" s="19"/>
       <c r="E68" s="17"/>
-      <c r="F68" s="43"/>
-      <c r="G68" s="39"/>
-      <c r="H68" s="55"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="42"/>
-      <c r="B69" s="42"/>
+      <c r="F68" s="39"/>
+      <c r="G68" s="41"/>
+      <c r="H68" s="56"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A69" s="48"/>
+      <c r="B69" s="48"/>
       <c r="C69" s="19"/>
       <c r="D69" s="19"/>
       <c r="E69" s="17"/>
-      <c r="F69" s="44"/>
-      <c r="G69" s="40"/>
-      <c r="H69" s="55"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="42"/>
-      <c r="B70" s="42"/>
+      <c r="F69" s="45"/>
+      <c r="G69" s="46"/>
+      <c r="H69" s="56"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A70" s="48"/>
+      <c r="B70" s="48"/>
       <c r="C70" s="19"/>
       <c r="D70" s="19"/>
       <c r="E70" s="17"/>
-      <c r="F70" s="44"/>
-      <c r="G70" s="40"/>
-      <c r="H70" s="55"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="42"/>
-      <c r="B71" s="42"/>
+      <c r="F70" s="45"/>
+      <c r="G70" s="46"/>
+      <c r="H70" s="56"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A71" s="48"/>
+      <c r="B71" s="48"/>
       <c r="C71" s="19"/>
       <c r="D71" s="19"/>
       <c r="E71" s="18"/>
-      <c r="F71" s="45"/>
-      <c r="G71" s="41"/>
-      <c r="H71" s="55"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" s="42"/>
-      <c r="B72" s="42"/>
+      <c r="F71" s="40"/>
+      <c r="G71" s="42"/>
+      <c r="H71" s="56"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" s="48"/>
+      <c r="B72" s="48"/>
       <c r="C72" s="19"/>
       <c r="D72" s="19"/>
       <c r="E72" s="17"/>
-      <c r="F72" s="43"/>
-      <c r="G72" s="39"/>
-      <c r="H72" s="55"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="42"/>
-      <c r="B73" s="42"/>
+      <c r="F72" s="39"/>
+      <c r="G72" s="41"/>
+      <c r="H72" s="56"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" s="48"/>
+      <c r="B73" s="48"/>
       <c r="C73" s="19"/>
       <c r="D73" s="19"/>
       <c r="E73" s="17"/>
-      <c r="F73" s="44"/>
-      <c r="G73" s="40"/>
-      <c r="H73" s="55"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="42"/>
-      <c r="B74" s="42"/>
+      <c r="F73" s="45"/>
+      <c r="G73" s="46"/>
+      <c r="H73" s="56"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" s="48"/>
+      <c r="B74" s="48"/>
       <c r="C74" s="19"/>
       <c r="D74" s="19"/>
       <c r="E74" s="18"/>
-      <c r="F74" s="45"/>
-      <c r="G74" s="41"/>
-      <c r="H74" s="55"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="42"/>
-      <c r="B75" s="42"/>
+      <c r="F74" s="40"/>
+      <c r="G74" s="42"/>
+      <c r="H74" s="56"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" s="48"/>
+      <c r="B75" s="48"/>
       <c r="C75" s="19"/>
       <c r="D75" s="19"/>
       <c r="E75" s="17"/>
-      <c r="F75" s="43"/>
+      <c r="F75" s="39"/>
       <c r="G75" s="51"/>
-      <c r="H75" s="55"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="42"/>
-      <c r="B76" s="42"/>
+      <c r="H75" s="56"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" s="48"/>
+      <c r="B76" s="48"/>
       <c r="C76" s="19"/>
       <c r="D76" s="19"/>
       <c r="E76" s="18"/>
-      <c r="F76" s="45"/>
+      <c r="F76" s="40"/>
       <c r="G76" s="52"/>
-      <c r="H76" s="55"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="42"/>
-      <c r="B77" s="42"/>
+      <c r="H76" s="56"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A77" s="48"/>
+      <c r="B77" s="48"/>
       <c r="C77" s="19"/>
       <c r="D77" s="19"/>
       <c r="E77" s="17"/>
-      <c r="F77" s="43"/>
-      <c r="G77" s="39"/>
-      <c r="H77" s="55"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="42"/>
-      <c r="B78" s="42"/>
+      <c r="F77" s="39"/>
+      <c r="G77" s="41"/>
+      <c r="H77" s="56"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A78" s="48"/>
+      <c r="B78" s="48"/>
       <c r="C78" s="19"/>
       <c r="D78" s="19"/>
       <c r="E78" s="18"/>
-      <c r="F78" s="45"/>
-      <c r="G78" s="41"/>
-      <c r="H78" s="55"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="42"/>
-      <c r="B79" s="42"/>
+      <c r="F78" s="40"/>
+      <c r="G78" s="42"/>
+      <c r="H78" s="56"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A79" s="48"/>
+      <c r="B79" s="48"/>
       <c r="C79" s="19"/>
       <c r="D79" s="19"/>
       <c r="E79" s="17"/>
-      <c r="F79" s="43"/>
-      <c r="G79" s="39"/>
-      <c r="H79" s="55"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="42"/>
-      <c r="B80" s="42"/>
+      <c r="F79" s="39"/>
+      <c r="G79" s="41"/>
+      <c r="H79" s="56"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" s="48"/>
+      <c r="B80" s="48"/>
       <c r="C80" s="19"/>
       <c r="D80" s="19"/>
       <c r="E80" s="17"/>
-      <c r="F80" s="44"/>
-      <c r="G80" s="40"/>
-      <c r="H80" s="55"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="42"/>
-      <c r="B81" s="42"/>
+      <c r="F80" s="45"/>
+      <c r="G80" s="46"/>
+      <c r="H80" s="56"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A81" s="48"/>
+      <c r="B81" s="48"/>
       <c r="C81" s="19"/>
       <c r="D81" s="19"/>
       <c r="E81" s="18"/>
-      <c r="F81" s="45"/>
-      <c r="G81" s="41"/>
-      <c r="H81" s="55"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="42"/>
-      <c r="B82" s="42"/>
+      <c r="F81" s="40"/>
+      <c r="G81" s="42"/>
+      <c r="H81" s="56"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A82" s="48"/>
+      <c r="B82" s="48"/>
       <c r="C82" s="19"/>
       <c r="D82" s="19"/>
       <c r="E82" s="17"/>
-      <c r="F82" s="43"/>
-      <c r="G82" s="39"/>
-      <c r="H82" s="55"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="42"/>
-      <c r="B83" s="42"/>
+      <c r="F82" s="39"/>
+      <c r="G82" s="41"/>
+      <c r="H82" s="56"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A83" s="48"/>
+      <c r="B83" s="48"/>
       <c r="C83" s="19"/>
       <c r="D83" s="19"/>
       <c r="E83" s="18"/>
-      <c r="F83" s="45"/>
-      <c r="G83" s="41"/>
-      <c r="H83" s="55"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="42"/>
-      <c r="B84" s="42"/>
+      <c r="F83" s="40"/>
+      <c r="G83" s="42"/>
+      <c r="H83" s="56"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A84" s="48"/>
+      <c r="B84" s="48"/>
       <c r="C84" s="19"/>
       <c r="D84" s="21"/>
       <c r="E84" s="17"/>
-      <c r="F84" s="43"/>
-      <c r="G84" s="39"/>
-      <c r="H84" s="55"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="42"/>
-      <c r="B85" s="42"/>
+      <c r="F84" s="39"/>
+      <c r="G84" s="41"/>
+      <c r="H84" s="56"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A85" s="48"/>
+      <c r="B85" s="48"/>
       <c r="C85" s="19"/>
       <c r="D85" s="21"/>
       <c r="E85" s="18"/>
-      <c r="F85" s="45"/>
-      <c r="G85" s="41"/>
-      <c r="H85" s="55"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="42"/>
-      <c r="B86" s="42"/>
+      <c r="F85" s="40"/>
+      <c r="G85" s="42"/>
+      <c r="H85" s="56"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A86" s="48"/>
+      <c r="B86" s="48"/>
       <c r="C86" s="19"/>
       <c r="D86" s="19"/>
       <c r="E86" s="17"/>
-      <c r="F86" s="43"/>
-      <c r="G86" s="39"/>
-      <c r="H86" s="55"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="42"/>
-      <c r="B87" s="42"/>
+      <c r="F86" s="39"/>
+      <c r="G86" s="41"/>
+      <c r="H86" s="56"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A87" s="48"/>
+      <c r="B87" s="48"/>
       <c r="C87" s="19"/>
       <c r="D87" s="19"/>
       <c r="E87" s="18"/>
-      <c r="F87" s="45"/>
-      <c r="G87" s="41"/>
-      <c r="H87" s="55"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="42"/>
-      <c r="B88" s="42"/>
+      <c r="F87" s="40"/>
+      <c r="G87" s="42"/>
+      <c r="H87" s="56"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A88" s="48"/>
+      <c r="B88" s="48"/>
       <c r="C88" s="19"/>
       <c r="D88" s="19"/>
       <c r="E88" s="17"/>
-      <c r="F88" s="43"/>
-      <c r="G88" s="39"/>
-      <c r="H88" s="55"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="42"/>
-      <c r="B89" s="42"/>
+      <c r="F88" s="39"/>
+      <c r="G88" s="41"/>
+      <c r="H88" s="56"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A89" s="48"/>
+      <c r="B89" s="48"/>
       <c r="C89" s="19"/>
       <c r="D89" s="19"/>
       <c r="E89" s="17"/>
-      <c r="F89" s="44"/>
-      <c r="G89" s="40"/>
-      <c r="H89" s="55"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="42"/>
-      <c r="B90" s="42"/>
+      <c r="F89" s="45"/>
+      <c r="G89" s="46"/>
+      <c r="H89" s="56"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A90" s="48"/>
+      <c r="B90" s="48"/>
       <c r="C90" s="19"/>
       <c r="D90" s="19"/>
       <c r="E90" s="18"/>
-      <c r="F90" s="45"/>
-      <c r="G90" s="41"/>
-      <c r="H90" s="55"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="42"/>
-      <c r="B91" s="42"/>
+      <c r="F90" s="40"/>
+      <c r="G90" s="42"/>
+      <c r="H90" s="56"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A91" s="48"/>
+      <c r="B91" s="48"/>
       <c r="C91" s="19"/>
       <c r="D91" s="21"/>
       <c r="E91" s="17"/>
-      <c r="F91" s="43"/>
-      <c r="G91" s="39"/>
-      <c r="H91" s="55"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="42"/>
-      <c r="B92" s="42"/>
+      <c r="F91" s="39"/>
+      <c r="G91" s="41"/>
+      <c r="H91" s="56"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A92" s="48"/>
+      <c r="B92" s="48"/>
       <c r="C92" s="19"/>
       <c r="D92" s="21"/>
       <c r="E92" s="18"/>
-      <c r="F92" s="45"/>
-      <c r="G92" s="41"/>
-      <c r="H92" s="55"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="42"/>
-      <c r="B93" s="42"/>
+      <c r="F92" s="40"/>
+      <c r="G92" s="42"/>
+      <c r="H92" s="56"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A93" s="48"/>
+      <c r="B93" s="48"/>
       <c r="C93" s="19"/>
       <c r="D93" s="21"/>
       <c r="E93" s="17"/>
-      <c r="F93" s="43"/>
-      <c r="G93" s="39"/>
-      <c r="H93" s="55"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="42"/>
-      <c r="B94" s="42"/>
+      <c r="F93" s="39"/>
+      <c r="G93" s="41"/>
+      <c r="H93" s="56"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A94" s="48"/>
+      <c r="B94" s="48"/>
       <c r="C94" s="19"/>
       <c r="D94" s="19"/>
       <c r="E94" s="17"/>
-      <c r="F94" s="44"/>
-      <c r="G94" s="40"/>
-      <c r="H94" s="55"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="42"/>
-      <c r="B95" s="42"/>
+      <c r="F94" s="45"/>
+      <c r="G94" s="46"/>
+      <c r="H94" s="56"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A95" s="48"/>
+      <c r="B95" s="48"/>
       <c r="C95" s="19"/>
       <c r="D95" s="19"/>
       <c r="E95" s="18"/>
-      <c r="F95" s="45"/>
-      <c r="G95" s="41"/>
-      <c r="H95" s="55"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="42"/>
-      <c r="B96" s="42"/>
+      <c r="F95" s="40"/>
+      <c r="G95" s="42"/>
+      <c r="H95" s="56"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A96" s="48"/>
+      <c r="B96" s="48"/>
       <c r="C96" s="19"/>
       <c r="D96" s="21"/>
       <c r="E96" s="17"/>
-      <c r="F96" s="43"/>
-      <c r="G96" s="39"/>
-      <c r="H96" s="55"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="42"/>
-      <c r="B97" s="42"/>
+      <c r="F96" s="39"/>
+      <c r="G96" s="41"/>
+      <c r="H96" s="56"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A97" s="48"/>
+      <c r="B97" s="48"/>
       <c r="C97" s="19"/>
       <c r="D97" s="21"/>
       <c r="E97" s="18"/>
-      <c r="F97" s="45"/>
-      <c r="G97" s="41"/>
-      <c r="H97" s="55"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="42"/>
-      <c r="B98" s="42"/>
+      <c r="F97" s="40"/>
+      <c r="G97" s="42"/>
+      <c r="H97" s="56"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A98" s="48"/>
+      <c r="B98" s="48"/>
       <c r="C98" s="19"/>
       <c r="D98" s="19"/>
       <c r="E98" s="17"/>
-      <c r="F98" s="43"/>
-      <c r="G98" s="39"/>
-      <c r="H98" s="55"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="42"/>
-      <c r="B99" s="42"/>
+      <c r="F98" s="39"/>
+      <c r="G98" s="41"/>
+      <c r="H98" s="56"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A99" s="48"/>
+      <c r="B99" s="48"/>
       <c r="C99" s="19"/>
       <c r="D99" s="19"/>
       <c r="E99" s="18"/>
-      <c r="F99" s="45"/>
-      <c r="G99" s="41"/>
-      <c r="H99" s="55"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="42"/>
-      <c r="B100" s="42"/>
+      <c r="F99" s="40"/>
+      <c r="G99" s="42"/>
+      <c r="H99" s="56"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A100" s="48"/>
+      <c r="B100" s="48"/>
       <c r="C100" s="19"/>
       <c r="D100" s="19"/>
       <c r="E100" s="17"/>
-      <c r="F100" s="43"/>
-      <c r="G100" s="39"/>
-      <c r="H100" s="55"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="42"/>
-      <c r="B101" s="42"/>
+      <c r="F100" s="39"/>
+      <c r="G100" s="41"/>
+      <c r="H100" s="56"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A101" s="48"/>
+      <c r="B101" s="48"/>
       <c r="C101" s="19"/>
       <c r="D101" s="19"/>
       <c r="E101" s="18"/>
-      <c r="F101" s="45"/>
-      <c r="G101" s="41"/>
-      <c r="H101" s="55"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="42"/>
-      <c r="B102" s="42"/>
+      <c r="F101" s="40"/>
+      <c r="G101" s="42"/>
+      <c r="H101" s="56"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A102" s="48"/>
+      <c r="B102" s="48"/>
       <c r="C102" s="19"/>
       <c r="D102" s="19"/>
       <c r="E102" s="17"/>
-      <c r="F102" s="43"/>
-      <c r="G102" s="39"/>
-      <c r="H102" s="55"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="42"/>
-      <c r="B103" s="42"/>
+      <c r="F102" s="39"/>
+      <c r="G102" s="41"/>
+      <c r="H102" s="56"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A103" s="48"/>
+      <c r="B103" s="48"/>
       <c r="C103" s="19"/>
       <c r="D103" s="19"/>
       <c r="E103" s="17"/>
-      <c r="F103" s="44"/>
-      <c r="G103" s="40"/>
-      <c r="H103" s="55"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="42"/>
-      <c r="B104" s="42"/>
+      <c r="F103" s="45"/>
+      <c r="G103" s="46"/>
+      <c r="H103" s="56"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A104" s="48"/>
+      <c r="B104" s="48"/>
       <c r="C104" s="19"/>
       <c r="D104" s="19"/>
       <c r="E104" s="18"/>
-      <c r="F104" s="45"/>
-      <c r="G104" s="41"/>
-      <c r="H104" s="55"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="42"/>
-      <c r="B105" s="42"/>
+      <c r="F104" s="40"/>
+      <c r="G104" s="42"/>
+      <c r="H104" s="56"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A105" s="48"/>
+      <c r="B105" s="48"/>
       <c r="C105" s="19"/>
       <c r="D105" s="21"/>
       <c r="E105" s="17"/>
-      <c r="F105" s="43"/>
-      <c r="G105" s="39"/>
-      <c r="H105" s="55"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="42"/>
-      <c r="B106" s="42"/>
+      <c r="F105" s="39"/>
+      <c r="G105" s="41"/>
+      <c r="H105" s="56"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A106" s="48"/>
+      <c r="B106" s="48"/>
       <c r="C106" s="19"/>
       <c r="D106" s="21"/>
       <c r="E106" s="18"/>
-      <c r="F106" s="45"/>
-      <c r="G106" s="41"/>
-      <c r="H106" s="55"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="42"/>
-      <c r="B107" s="42"/>
+      <c r="F106" s="40"/>
+      <c r="G106" s="42"/>
+      <c r="H106" s="56"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A107" s="48"/>
+      <c r="B107" s="48"/>
       <c r="C107" s="19"/>
       <c r="D107" s="19"/>
       <c r="E107" s="17"/>
-      <c r="F107" s="43"/>
-      <c r="G107" s="39"/>
-      <c r="H107" s="55"/>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="42"/>
-      <c r="B108" s="42"/>
+      <c r="F107" s="39"/>
+      <c r="G107" s="41"/>
+      <c r="H107" s="56"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A108" s="48"/>
+      <c r="B108" s="48"/>
       <c r="C108" s="19"/>
       <c r="D108" s="19"/>
       <c r="E108" s="17"/>
-      <c r="F108" s="44"/>
-      <c r="G108" s="40"/>
-      <c r="H108" s="55"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="42"/>
-      <c r="B109" s="42"/>
+      <c r="F108" s="45"/>
+      <c r="G108" s="46"/>
+      <c r="H108" s="56"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A109" s="48"/>
+      <c r="B109" s="48"/>
       <c r="C109" s="19"/>
       <c r="D109" s="19"/>
       <c r="E109" s="18"/>
-      <c r="F109" s="45"/>
-      <c r="G109" s="41"/>
-      <c r="H109" s="55"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="42"/>
-      <c r="B110" s="42"/>
+      <c r="F109" s="40"/>
+      <c r="G109" s="42"/>
+      <c r="H109" s="56"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A110" s="48"/>
+      <c r="B110" s="48"/>
       <c r="C110" s="19"/>
       <c r="D110" s="19"/>
       <c r="E110" s="17"/>
-      <c r="F110" s="43"/>
-      <c r="G110" s="39"/>
-      <c r="H110" s="55"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="42"/>
-      <c r="B111" s="42"/>
+      <c r="F110" s="39"/>
+      <c r="G110" s="41"/>
+      <c r="H110" s="56"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A111" s="48"/>
+      <c r="B111" s="48"/>
       <c r="C111" s="19"/>
       <c r="D111" s="19"/>
       <c r="E111" s="18"/>
-      <c r="F111" s="45"/>
-      <c r="G111" s="41"/>
-      <c r="H111" s="55"/>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="47"/>
-      <c r="B112" s="47"/>
+      <c r="F111" s="40"/>
+      <c r="G111" s="42"/>
+      <c r="H111" s="56"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A112" s="49"/>
+      <c r="B112" s="49"/>
       <c r="C112" s="19"/>
       <c r="D112" s="19"/>
       <c r="E112" s="17"/>
-      <c r="F112" s="43"/>
-      <c r="G112" s="39"/>
-      <c r="H112" s="55"/>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="48"/>
-      <c r="B113" s="48"/>
+      <c r="F112" s="39"/>
+      <c r="G112" s="41"/>
+      <c r="H112" s="56"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A113" s="54"/>
+      <c r="B113" s="54"/>
       <c r="C113" s="19"/>
       <c r="D113" s="19"/>
       <c r="E113" s="17"/>
-      <c r="F113" s="44"/>
-      <c r="G113" s="40"/>
-      <c r="H113" s="55"/>
-    </row>
-    <row r="114" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="49"/>
-      <c r="B114" s="49"/>
+      <c r="F113" s="45"/>
+      <c r="G113" s="46"/>
+      <c r="H113" s="56"/>
+    </row>
+    <row r="114" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="50"/>
+      <c r="B114" s="50"/>
       <c r="D114" s="19"/>
       <c r="E114" s="18"/>
-      <c r="F114" s="45"/>
-      <c r="G114" s="41"/>
-      <c r="H114" s="55"/>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="42"/>
-      <c r="B115" s="42"/>
+      <c r="F114" s="40"/>
+      <c r="G114" s="42"/>
+      <c r="H114" s="56"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A115" s="48"/>
+      <c r="B115" s="48"/>
       <c r="C115" s="19"/>
       <c r="D115" s="19"/>
       <c r="E115" s="17"/>
-      <c r="F115" s="43"/>
-      <c r="G115" s="39"/>
-      <c r="H115" s="55"/>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="42"/>
-      <c r="B116" s="42"/>
+      <c r="F115" s="39"/>
+      <c r="G115" s="41"/>
+      <c r="H115" s="56"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A116" s="48"/>
+      <c r="B116" s="48"/>
       <c r="C116" s="19"/>
       <c r="D116" s="19"/>
       <c r="E116" s="18"/>
-      <c r="F116" s="45"/>
-      <c r="G116" s="41"/>
-      <c r="H116" s="55"/>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="42"/>
-      <c r="B117" s="42"/>
+      <c r="F116" s="40"/>
+      <c r="G116" s="42"/>
+      <c r="H116" s="56"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A117" s="48"/>
+      <c r="B117" s="48"/>
       <c r="C117" s="19"/>
       <c r="D117" s="21"/>
       <c r="E117" s="17"/>
-      <c r="F117" s="43"/>
-      <c r="G117" s="39"/>
-      <c r="H117" s="55"/>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="42"/>
-      <c r="B118" s="42"/>
+      <c r="F117" s="39"/>
+      <c r="G117" s="41"/>
+      <c r="H117" s="56"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A118" s="48"/>
+      <c r="B118" s="48"/>
       <c r="C118" s="19"/>
       <c r="D118" s="21"/>
       <c r="E118" s="18"/>
-      <c r="F118" s="45"/>
-      <c r="G118" s="41"/>
-      <c r="H118" s="55"/>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="47"/>
-      <c r="B119" s="47"/>
+      <c r="F118" s="40"/>
+      <c r="G118" s="42"/>
+      <c r="H118" s="56"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A119" s="49"/>
+      <c r="B119" s="49"/>
       <c r="C119" s="19"/>
       <c r="D119" s="21"/>
       <c r="E119" s="17"/>
-      <c r="F119" s="37"/>
-      <c r="G119" s="38"/>
-      <c r="H119" s="55"/>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="48"/>
-      <c r="B120" s="48"/>
+      <c r="F119" s="44"/>
+      <c r="G119" s="47"/>
+      <c r="H119" s="56"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A120" s="54"/>
+      <c r="B120" s="54"/>
       <c r="C120" s="19"/>
       <c r="D120" s="21"/>
       <c r="E120" s="17"/>
-      <c r="F120" s="37"/>
-      <c r="G120" s="38"/>
-      <c r="H120" s="55"/>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="49"/>
-      <c r="B121" s="49"/>
+      <c r="F120" s="44"/>
+      <c r="G120" s="47"/>
+      <c r="H120" s="56"/>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A121" s="50"/>
+      <c r="B121" s="50"/>
       <c r="C121" s="19"/>
       <c r="D121" s="21"/>
       <c r="E121" s="18"/>
-      <c r="F121" s="37"/>
-      <c r="G121" s="38"/>
-      <c r="H121" s="55"/>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="42"/>
-      <c r="B122" s="42"/>
+      <c r="F121" s="44"/>
+      <c r="G121" s="47"/>
+      <c r="H121" s="56"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A122" s="48"/>
+      <c r="B122" s="48"/>
       <c r="C122" s="19"/>
       <c r="D122" s="19"/>
       <c r="E122" s="17"/>
-      <c r="F122" s="43"/>
-      <c r="G122" s="39"/>
-      <c r="H122" s="55"/>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="42"/>
-      <c r="B123" s="42"/>
+      <c r="F122" s="39"/>
+      <c r="G122" s="41"/>
+      <c r="H122" s="56"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A123" s="48"/>
+      <c r="B123" s="48"/>
       <c r="C123" s="19"/>
       <c r="D123" s="19"/>
       <c r="E123" s="17"/>
-      <c r="F123" s="44"/>
-      <c r="G123" s="40"/>
-      <c r="H123" s="55"/>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="42"/>
-      <c r="B124" s="42"/>
+      <c r="F123" s="45"/>
+      <c r="G123" s="46"/>
+      <c r="H123" s="56"/>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A124" s="48"/>
+      <c r="B124" s="48"/>
       <c r="C124" s="19"/>
       <c r="D124" s="19"/>
       <c r="E124" s="18"/>
-      <c r="F124" s="45"/>
-      <c r="G124" s="41"/>
-      <c r="H124" s="55"/>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="42"/>
-      <c r="B125" s="42"/>
+      <c r="F124" s="40"/>
+      <c r="G124" s="42"/>
+      <c r="H124" s="56"/>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A125" s="48"/>
+      <c r="B125" s="48"/>
       <c r="C125" s="19"/>
       <c r="D125" s="19"/>
       <c r="E125" s="17"/>
-      <c r="F125" s="43"/>
-      <c r="G125" s="39"/>
-      <c r="H125" s="55"/>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="42"/>
-      <c r="B126" s="42"/>
+      <c r="F125" s="39"/>
+      <c r="G125" s="41"/>
+      <c r="H125" s="56"/>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A126" s="48"/>
+      <c r="B126" s="48"/>
       <c r="C126" s="19"/>
       <c r="D126" s="19"/>
       <c r="E126" s="17"/>
-      <c r="F126" s="44"/>
-      <c r="G126" s="40"/>
-      <c r="H126" s="55"/>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="42"/>
-      <c r="B127" s="42"/>
+      <c r="F126" s="45"/>
+      <c r="G126" s="46"/>
+      <c r="H126" s="56"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A127" s="48"/>
+      <c r="B127" s="48"/>
       <c r="C127" s="19"/>
       <c r="D127" s="19"/>
       <c r="E127" s="18"/>
-      <c r="F127" s="45"/>
-      <c r="G127" s="41"/>
-      <c r="H127" s="55"/>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="42"/>
-      <c r="B128" s="42"/>
+      <c r="F127" s="40"/>
+      <c r="G127" s="42"/>
+      <c r="H127" s="56"/>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A128" s="48"/>
+      <c r="B128" s="48"/>
       <c r="C128" s="19"/>
       <c r="D128" s="19"/>
       <c r="E128" s="17"/>
-      <c r="F128" s="43"/>
-      <c r="G128" s="39"/>
-      <c r="H128" s="55"/>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="42"/>
-      <c r="B129" s="42"/>
+      <c r="F128" s="39"/>
+      <c r="G128" s="41"/>
+      <c r="H128" s="56"/>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A129" s="48"/>
+      <c r="B129" s="48"/>
       <c r="C129" s="19"/>
       <c r="D129" s="19"/>
       <c r="E129" s="18"/>
-      <c r="F129" s="45"/>
-      <c r="G129" s="41"/>
-      <c r="H129" s="55"/>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="42"/>
-      <c r="B130" s="42"/>
+      <c r="F129" s="40"/>
+      <c r="G129" s="42"/>
+      <c r="H129" s="56"/>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A130" s="48"/>
+      <c r="B130" s="48"/>
       <c r="C130" s="19"/>
       <c r="D130" s="19"/>
       <c r="E130" s="17"/>
-      <c r="F130" s="43"/>
-      <c r="G130" s="39"/>
-      <c r="H130" s="55"/>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="42"/>
-      <c r="B131" s="42"/>
+      <c r="F130" s="39"/>
+      <c r="G130" s="41"/>
+      <c r="H130" s="56"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A131" s="48"/>
+      <c r="B131" s="48"/>
       <c r="C131" s="19"/>
       <c r="D131" s="19"/>
       <c r="E131" s="17"/>
-      <c r="F131" s="44"/>
-      <c r="G131" s="40"/>
-      <c r="H131" s="55"/>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132" s="42"/>
-      <c r="B132" s="42"/>
+      <c r="F131" s="45"/>
+      <c r="G131" s="46"/>
+      <c r="H131" s="56"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A132" s="48"/>
+      <c r="B132" s="48"/>
       <c r="C132" s="19"/>
       <c r="D132" s="19"/>
       <c r="E132" s="18"/>
-      <c r="F132" s="45"/>
-      <c r="G132" s="41"/>
-      <c r="H132" s="55"/>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A133" s="42"/>
-      <c r="B133" s="42"/>
+      <c r="F132" s="40"/>
+      <c r="G132" s="42"/>
+      <c r="H132" s="56"/>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A133" s="48"/>
+      <c r="B133" s="48"/>
       <c r="C133" s="19"/>
       <c r="D133" s="21"/>
       <c r="E133" s="17"/>
-      <c r="F133" s="43"/>
-      <c r="G133" s="39"/>
-      <c r="H133" s="55"/>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134" s="42"/>
-      <c r="B134" s="42"/>
+      <c r="F133" s="39"/>
+      <c r="G133" s="41"/>
+      <c r="H133" s="56"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A134" s="48"/>
+      <c r="B134" s="48"/>
       <c r="C134" s="19"/>
       <c r="D134" s="21"/>
       <c r="E134" s="17"/>
-      <c r="F134" s="44"/>
-      <c r="G134" s="40"/>
-      <c r="H134" s="55"/>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="42"/>
-      <c r="B135" s="42"/>
+      <c r="F134" s="45"/>
+      <c r="G134" s="46"/>
+      <c r="H134" s="56"/>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A135" s="48"/>
+      <c r="B135" s="48"/>
       <c r="C135" s="19"/>
       <c r="D135" s="21"/>
       <c r="E135" s="18"/>
-      <c r="F135" s="45"/>
-      <c r="G135" s="41"/>
-      <c r="H135" s="55"/>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136" s="42"/>
-      <c r="B136" s="42"/>
+      <c r="F135" s="40"/>
+      <c r="G135" s="42"/>
+      <c r="H135" s="56"/>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A136" s="48"/>
+      <c r="B136" s="48"/>
       <c r="C136" s="19"/>
       <c r="D136" s="19"/>
       <c r="E136" s="17"/>
-      <c r="F136" s="43"/>
-      <c r="G136" s="39"/>
-      <c r="H136" s="55"/>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137" s="42"/>
-      <c r="B137" s="42"/>
+      <c r="F136" s="39"/>
+      <c r="G136" s="41"/>
+      <c r="H136" s="56"/>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A137" s="48"/>
+      <c r="B137" s="48"/>
       <c r="C137" s="19"/>
       <c r="D137" s="21"/>
       <c r="E137" s="17"/>
-      <c r="F137" s="44"/>
-      <c r="G137" s="40"/>
-      <c r="H137" s="55"/>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A138" s="42"/>
-      <c r="B138" s="42"/>
+      <c r="F137" s="45"/>
+      <c r="G137" s="46"/>
+      <c r="H137" s="56"/>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A138" s="48"/>
+      <c r="B138" s="48"/>
       <c r="C138" s="19"/>
       <c r="D138" s="21"/>
       <c r="E138" s="18"/>
-      <c r="F138" s="45"/>
-      <c r="G138" s="41"/>
-      <c r="H138" s="55"/>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A139" s="42"/>
-      <c r="B139" s="42"/>
+      <c r="F138" s="40"/>
+      <c r="G138" s="42"/>
+      <c r="H138" s="56"/>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A139" s="48"/>
+      <c r="B139" s="48"/>
       <c r="C139" s="19"/>
       <c r="D139" s="21"/>
       <c r="E139" s="17"/>
-      <c r="F139" s="43"/>
-      <c r="G139" s="39"/>
-      <c r="H139" s="55"/>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="42"/>
-      <c r="B140" s="42"/>
+      <c r="F139" s="39"/>
+      <c r="G139" s="41"/>
+      <c r="H139" s="56"/>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A140" s="48"/>
+      <c r="B140" s="48"/>
       <c r="C140" s="19"/>
       <c r="D140" s="21"/>
       <c r="E140" s="17"/>
-      <c r="F140" s="44"/>
-      <c r="G140" s="40"/>
-      <c r="H140" s="55"/>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" s="42"/>
-      <c r="B141" s="42"/>
+      <c r="F140" s="45"/>
+      <c r="G140" s="46"/>
+      <c r="H140" s="56"/>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A141" s="48"/>
+      <c r="B141" s="48"/>
       <c r="C141" s="19"/>
       <c r="D141" s="21"/>
       <c r="E141" s="18"/>
-      <c r="F141" s="45"/>
-      <c r="G141" s="41"/>
-      <c r="H141" s="55"/>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="42"/>
-      <c r="B142" s="42"/>
+      <c r="F141" s="40"/>
+      <c r="G141" s="42"/>
+      <c r="H141" s="56"/>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A142" s="48"/>
+      <c r="B142" s="48"/>
       <c r="C142" s="19"/>
       <c r="D142" s="21"/>
       <c r="E142" s="17"/>
-      <c r="F142" s="43"/>
-      <c r="G142" s="39"/>
-      <c r="H142" s="55"/>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A143" s="42"/>
-      <c r="B143" s="42"/>
+      <c r="F142" s="39"/>
+      <c r="G142" s="41"/>
+      <c r="H142" s="56"/>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A143" s="48"/>
+      <c r="B143" s="48"/>
       <c r="C143" s="19"/>
       <c r="D143" s="21"/>
       <c r="E143" s="17"/>
-      <c r="F143" s="44"/>
-      <c r="G143" s="40"/>
-      <c r="H143" s="55"/>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A144" s="42"/>
-      <c r="B144" s="42"/>
+      <c r="F143" s="45"/>
+      <c r="G143" s="46"/>
+      <c r="H143" s="56"/>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A144" s="48"/>
+      <c r="B144" s="48"/>
       <c r="C144" s="19"/>
       <c r="D144" s="21"/>
       <c r="E144" s="18"/>
-      <c r="F144" s="45"/>
-      <c r="G144" s="41"/>
-      <c r="H144" s="55"/>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145" s="42"/>
-      <c r="B145" s="42"/>
+      <c r="F144" s="40"/>
+      <c r="G144" s="42"/>
+      <c r="H144" s="56"/>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A145" s="48"/>
+      <c r="B145" s="48"/>
       <c r="C145" s="19"/>
       <c r="D145" s="21"/>
       <c r="E145" s="17"/>
-      <c r="F145" s="43"/>
-      <c r="G145" s="39"/>
-      <c r="H145" s="55"/>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="42"/>
-      <c r="B146" s="42"/>
+      <c r="F145" s="39"/>
+      <c r="G145" s="41"/>
+      <c r="H145" s="56"/>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A146" s="48"/>
+      <c r="B146" s="48"/>
       <c r="C146" s="19"/>
       <c r="D146" s="21"/>
       <c r="E146" s="18"/>
-      <c r="F146" s="44"/>
-      <c r="G146" s="40"/>
-      <c r="H146" s="55"/>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" s="42"/>
-      <c r="B147" s="42"/>
+      <c r="F146" s="45"/>
+      <c r="G146" s="46"/>
+      <c r="H146" s="56"/>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A147" s="48"/>
+      <c r="B147" s="48"/>
       <c r="C147" s="19"/>
       <c r="D147" s="21"/>
       <c r="E147" s="18"/>
-      <c r="F147" s="45"/>
-      <c r="G147" s="41"/>
-      <c r="H147" s="55"/>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A148" s="46"/>
-      <c r="B148" s="36"/>
+      <c r="F147" s="40"/>
+      <c r="G147" s="42"/>
+      <c r="H147" s="56"/>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A148" s="38"/>
+      <c r="B148" s="43"/>
       <c r="C148" s="24"/>
       <c r="D148" s="21"/>
       <c r="E148" s="18"/>
-      <c r="F148" s="43"/>
-      <c r="G148" s="39"/>
-      <c r="H148" s="55"/>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" s="46"/>
-      <c r="B149" s="36"/>
+      <c r="F148" s="39"/>
+      <c r="G148" s="41"/>
+      <c r="H148" s="56"/>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A149" s="38"/>
+      <c r="B149" s="43"/>
       <c r="C149" s="19"/>
       <c r="D149" s="21"/>
       <c r="E149" s="18"/>
-      <c r="F149" s="45"/>
-      <c r="G149" s="41"/>
-      <c r="H149" s="55"/>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A150" s="46"/>
-      <c r="B150" s="42"/>
+      <c r="F149" s="40"/>
+      <c r="G149" s="42"/>
+      <c r="H149" s="56"/>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A150" s="38"/>
+      <c r="B150" s="48"/>
       <c r="C150" s="19"/>
       <c r="D150" s="21"/>
       <c r="E150" s="18"/>
-      <c r="F150" s="43"/>
-      <c r="G150" s="39"/>
-      <c r="H150" s="55"/>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A151" s="46"/>
-      <c r="B151" s="42"/>
+      <c r="F150" s="39"/>
+      <c r="G150" s="41"/>
+      <c r="H150" s="56"/>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A151" s="38"/>
+      <c r="B151" s="48"/>
       <c r="C151" s="19"/>
       <c r="D151" s="21"/>
       <c r="E151" s="18"/>
-      <c r="F151" s="45"/>
-      <c r="G151" s="41"/>
-      <c r="H151" s="55"/>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A152" s="46"/>
-      <c r="B152" s="42"/>
+      <c r="F151" s="40"/>
+      <c r="G151" s="42"/>
+      <c r="H151" s="56"/>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A152" s="38"/>
+      <c r="B152" s="48"/>
       <c r="C152" s="24"/>
       <c r="D152" s="21"/>
       <c r="E152" s="18"/>
-      <c r="F152" s="43"/>
-      <c r="G152" s="39"/>
-      <c r="H152" s="55"/>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A153" s="46"/>
-      <c r="B153" s="42"/>
+      <c r="F152" s="39"/>
+      <c r="G152" s="41"/>
+      <c r="H152" s="56"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A153" s="38"/>
+      <c r="B153" s="48"/>
       <c r="C153" s="19"/>
       <c r="D153" s="21"/>
       <c r="E153" s="18"/>
-      <c r="F153" s="45"/>
-      <c r="G153" s="41"/>
-      <c r="H153" s="55"/>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A154" s="46"/>
-      <c r="B154" s="42"/>
+      <c r="F153" s="40"/>
+      <c r="G153" s="42"/>
+      <c r="H153" s="56"/>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A154" s="38"/>
+      <c r="B154" s="48"/>
       <c r="C154" s="19"/>
       <c r="D154" s="21"/>
       <c r="E154" s="18"/>
-      <c r="F154" s="43"/>
-      <c r="G154" s="39"/>
-      <c r="H154" s="55"/>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A155" s="46"/>
-      <c r="B155" s="42"/>
+      <c r="F154" s="39"/>
+      <c r="G154" s="41"/>
+      <c r="H154" s="56"/>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A155" s="38"/>
+      <c r="B155" s="48"/>
       <c r="C155" s="19"/>
       <c r="D155" s="21"/>
       <c r="E155" s="18"/>
-      <c r="F155" s="44"/>
-      <c r="G155" s="40"/>
-      <c r="H155" s="55"/>
-    </row>
-    <row r="156" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="46"/>
-      <c r="B156" s="42"/>
+      <c r="F155" s="45"/>
+      <c r="G155" s="46"/>
+      <c r="H155" s="56"/>
+    </row>
+    <row r="156" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A156" s="38"/>
+      <c r="B156" s="48"/>
       <c r="C156" s="19"/>
       <c r="D156" s="19"/>
       <c r="E156" s="18"/>
-      <c r="F156" s="45"/>
-      <c r="G156" s="41"/>
-      <c r="H156" s="55"/>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A157" s="46"/>
-      <c r="B157" s="42"/>
+      <c r="F156" s="40"/>
+      <c r="G156" s="42"/>
+      <c r="H156" s="56"/>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A157" s="38"/>
+      <c r="B157" s="48"/>
       <c r="C157" s="19"/>
       <c r="D157" s="19"/>
       <c r="E157" s="18"/>
-      <c r="F157" s="43"/>
-      <c r="G157" s="39"/>
-      <c r="H157" s="55"/>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A158" s="46"/>
-      <c r="B158" s="42"/>
+      <c r="F157" s="39"/>
+      <c r="G157" s="41"/>
+      <c r="H157" s="56"/>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A158" s="38"/>
+      <c r="B158" s="48"/>
       <c r="C158" s="19"/>
       <c r="D158" s="21"/>
       <c r="E158" s="18"/>
-      <c r="F158" s="45"/>
-      <c r="G158" s="41"/>
-      <c r="H158" s="55"/>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A159" s="46"/>
-      <c r="B159" s="38"/>
+      <c r="F158" s="40"/>
+      <c r="G158" s="42"/>
+      <c r="H158" s="56"/>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A159" s="38"/>
+      <c r="B159" s="47"/>
       <c r="C159" s="24"/>
       <c r="D159" s="25"/>
       <c r="E159" s="17"/>
-      <c r="F159" s="43"/>
-      <c r="G159" s="39"/>
-      <c r="H159" s="55"/>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A160" s="46"/>
-      <c r="B160" s="38"/>
+      <c r="F159" s="39"/>
+      <c r="G159" s="41"/>
+      <c r="H159" s="56"/>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A160" s="38"/>
+      <c r="B160" s="47"/>
       <c r="C160" s="19"/>
       <c r="D160" s="21"/>
       <c r="E160" s="18"/>
-      <c r="F160" s="45"/>
-      <c r="G160" s="41"/>
-      <c r="H160" s="55"/>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A161" s="42"/>
-      <c r="B161" s="47"/>
+      <c r="F160" s="40"/>
+      <c r="G160" s="42"/>
+      <c r="H160" s="56"/>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A161" s="48"/>
+      <c r="B161" s="49"/>
       <c r="C161" s="19"/>
       <c r="D161" s="21"/>
       <c r="E161" s="17"/>
-      <c r="F161" s="43"/>
-      <c r="G161" s="39"/>
-      <c r="H161" s="55"/>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A162" s="42"/>
-      <c r="B162" s="49"/>
+      <c r="F161" s="39"/>
+      <c r="G161" s="41"/>
+      <c r="H161" s="56"/>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A162" s="48"/>
+      <c r="B162" s="50"/>
       <c r="C162" s="19"/>
       <c r="D162" s="21"/>
       <c r="E162" s="18"/>
-      <c r="F162" s="45"/>
-      <c r="G162" s="41"/>
-      <c r="H162" s="55"/>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A163" s="46"/>
-      <c r="B163" s="36"/>
+      <c r="F162" s="40"/>
+      <c r="G162" s="42"/>
+      <c r="H162" s="56"/>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A163" s="38"/>
+      <c r="B163" s="43"/>
       <c r="C163" s="19"/>
       <c r="D163" s="25"/>
       <c r="E163" s="17"/>
-      <c r="F163" s="43"/>
-      <c r="G163" s="39"/>
-      <c r="H163" s="55"/>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A164" s="46"/>
-      <c r="B164" s="36"/>
+      <c r="F163" s="39"/>
+      <c r="G163" s="41"/>
+      <c r="H163" s="56"/>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A164" s="38"/>
+      <c r="B164" s="43"/>
       <c r="C164" s="19"/>
       <c r="D164" s="21"/>
       <c r="E164" s="18"/>
-      <c r="F164" s="45"/>
-      <c r="G164" s="41"/>
-      <c r="H164" s="55"/>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A165" s="46"/>
-      <c r="B165" s="38"/>
+      <c r="F164" s="40"/>
+      <c r="G164" s="42"/>
+      <c r="H164" s="56"/>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A165" s="38"/>
+      <c r="B165" s="47"/>
       <c r="C165" s="24"/>
       <c r="D165" s="21"/>
       <c r="E165" s="17"/>
-      <c r="F165" s="43"/>
-      <c r="G165" s="39"/>
-      <c r="H165" s="55"/>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A166" s="46"/>
-      <c r="B166" s="38"/>
+      <c r="F165" s="39"/>
+      <c r="G165" s="41"/>
+      <c r="H165" s="56"/>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A166" s="38"/>
+      <c r="B166" s="47"/>
       <c r="C166" s="19"/>
       <c r="D166" s="21"/>
       <c r="E166" s="17"/>
-      <c r="F166" s="44"/>
-      <c r="G166" s="40"/>
-      <c r="H166" s="55"/>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A167" s="46"/>
-      <c r="B167" s="38"/>
+      <c r="F166" s="45"/>
+      <c r="G166" s="46"/>
+      <c r="H166" s="56"/>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A167" s="38"/>
+      <c r="B167" s="47"/>
       <c r="C167" s="19"/>
       <c r="D167" s="21"/>
       <c r="E167" s="18"/>
-      <c r="F167" s="45"/>
-      <c r="G167" s="41"/>
-      <c r="H167" s="55"/>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" s="46"/>
-      <c r="B168" s="36"/>
+      <c r="F167" s="40"/>
+      <c r="G167" s="42"/>
+      <c r="H167" s="56"/>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A168" s="38"/>
+      <c r="B168" s="43"/>
       <c r="C168" s="19"/>
       <c r="D168" s="21"/>
       <c r="E168" s="17"/>
-      <c r="F168" s="43"/>
-      <c r="G168" s="39"/>
-      <c r="H168" s="55"/>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A169" s="46"/>
-      <c r="B169" s="36"/>
+      <c r="F168" s="39"/>
+      <c r="G168" s="41"/>
+      <c r="H168" s="56"/>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A169" s="38"/>
+      <c r="B169" s="43"/>
       <c r="C169" s="19"/>
       <c r="D169" s="21"/>
       <c r="E169" s="18"/>
-      <c r="F169" s="45"/>
-      <c r="G169" s="41"/>
-      <c r="H169" s="55"/>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A170" s="46"/>
-      <c r="B170" s="36"/>
+      <c r="F169" s="40"/>
+      <c r="G169" s="42"/>
+      <c r="H169" s="56"/>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A170" s="38"/>
+      <c r="B170" s="43"/>
       <c r="C170" s="24"/>
       <c r="D170" s="25"/>
       <c r="E170" s="17"/>
-      <c r="F170" s="43"/>
-      <c r="G170" s="39"/>
-      <c r="H170" s="55"/>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A171" s="46"/>
-      <c r="B171" s="36"/>
+      <c r="F170" s="39"/>
+      <c r="G170" s="41"/>
+      <c r="H170" s="56"/>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A171" s="38"/>
+      <c r="B171" s="43"/>
       <c r="C171" s="19"/>
       <c r="D171" s="21"/>
       <c r="E171" s="18"/>
-      <c r="F171" s="45"/>
-      <c r="G171" s="41"/>
-      <c r="H171" s="55"/>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A172" s="46"/>
-      <c r="B172" s="36"/>
+      <c r="F171" s="40"/>
+      <c r="G171" s="42"/>
+      <c r="H171" s="56"/>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A172" s="38"/>
+      <c r="B172" s="43"/>
       <c r="C172" s="19"/>
       <c r="D172" s="21"/>
       <c r="E172" s="17"/>
-      <c r="F172" s="43"/>
-      <c r="G172" s="39"/>
-      <c r="H172" s="55"/>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A173" s="46"/>
-      <c r="B173" s="36"/>
+      <c r="F172" s="39"/>
+      <c r="G172" s="41"/>
+      <c r="H172" s="56"/>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A173" s="38"/>
+      <c r="B173" s="43"/>
       <c r="C173" s="19"/>
       <c r="D173" s="21"/>
       <c r="E173" s="18"/>
-      <c r="F173" s="45"/>
-      <c r="G173" s="41"/>
-      <c r="H173" s="55"/>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A174" s="46"/>
-      <c r="B174" s="37"/>
+      <c r="F173" s="40"/>
+      <c r="G173" s="42"/>
+      <c r="H173" s="56"/>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A174" s="38"/>
+      <c r="B174" s="44"/>
       <c r="C174" s="24"/>
       <c r="D174" s="25"/>
       <c r="E174" s="17"/>
-      <c r="F174" s="43"/>
-      <c r="G174" s="39"/>
-      <c r="H174" s="55"/>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A175" s="46"/>
-      <c r="B175" s="37"/>
+      <c r="F174" s="39"/>
+      <c r="G174" s="41"/>
+      <c r="H174" s="56"/>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A175" s="38"/>
+      <c r="B175" s="44"/>
       <c r="C175" s="19"/>
       <c r="D175" s="21"/>
       <c r="E175" s="17"/>
-      <c r="F175" s="44"/>
-      <c r="G175" s="40"/>
-      <c r="H175" s="55"/>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A176" s="46"/>
-      <c r="B176" s="37"/>
+      <c r="F175" s="45"/>
+      <c r="G175" s="46"/>
+      <c r="H175" s="56"/>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A176" s="38"/>
+      <c r="B176" s="44"/>
       <c r="C176" s="18"/>
       <c r="D176" s="21"/>
       <c r="E176" s="18"/>
-      <c r="F176" s="45"/>
-      <c r="G176" s="41"/>
-      <c r="H176" s="56"/>
-    </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F176" s="40"/>
+      <c r="G176" s="42"/>
+      <c r="H176" s="57"/>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A177" s="32"/>
       <c r="B177" s="33"/>
       <c r="D177" s="14"/>
       <c r="F177" s="4"/>
       <c r="G177" s="31"/>
     </row>
-    <row r="178" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="34"/>
       <c r="B178" s="34"/>
       <c r="D178" s="14"/>
@@ -2775,7 +2793,7 @@
       <c r="F178" s="4"/>
       <c r="G178" s="15"/>
     </row>
-    <row r="179" spans="1:8" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" ht="36" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="35"/>
       <c r="B179" s="32"/>
       <c r="D179" s="28" t="s">
@@ -2793,267 +2811,299 @@
         <v>36</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" ht="18" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A180" s="35"/>
       <c r="B180" s="32"/>
       <c r="F180" s="6"/>
       <c r="G180" s="7"/>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A181" s="35"/>
       <c r="B181" s="32"/>
       <c r="E181" s="26"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B182"/>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B183" s="3"/>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B184" s="3"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B185" s="3"/>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B186" s="3"/>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B187" s="3"/>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B188" s="3"/>
       <c r="E188" s="16"/>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B189" s="3"/>
       <c r="E189" s="16"/>
       <c r="F189"/>
       <c r="H189"/>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B190" s="23"/>
       <c r="E190" s="16"/>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B191" s="23"/>
       <c r="E191" s="16"/>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B192" s="23"/>
       <c r="E192" s="16"/>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" s="13"/>
       <c r="B193" s="23"/>
       <c r="E193" s="16"/>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" s="13"/>
       <c r="B194" s="23"/>
       <c r="E194" s="16"/>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" s="13"/>
       <c r="B195" s="23"/>
       <c r="E195" s="16"/>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" s="13"/>
       <c r="B196" s="23"/>
       <c r="E196" s="16"/>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" s="13"/>
       <c r="B197" s="23"/>
       <c r="E197" s="16"/>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" s="13"/>
       <c r="B198" s="23"/>
       <c r="E198" s="16"/>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" s="13"/>
       <c r="B199" s="23"/>
       <c r="E199" s="16"/>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" s="13"/>
       <c r="B200" s="23"/>
       <c r="E200" s="16"/>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" s="13"/>
       <c r="B201" s="23"/>
       <c r="E201" s="16"/>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" s="13"/>
       <c r="B202" s="23"/>
       <c r="E202" s="16"/>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" s="13"/>
       <c r="B203" s="23"/>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" s="13"/>
       <c r="B204" s="23"/>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" s="13"/>
       <c r="B205" s="23"/>
       <c r="D205"/>
       <c r="E205"/>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" s="13"/>
       <c r="B206" s="23"/>
       <c r="C206"/>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" s="13"/>
       <c r="B207" s="23"/>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B208" s="23"/>
     </row>
-    <row r="209" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B209" s="23"/>
     </row>
-    <row r="210" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B210" s="23"/>
       <c r="C210"/>
     </row>
-    <row r="211" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B211" s="23"/>
     </row>
-    <row r="212" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B212" s="23"/>
     </row>
-    <row r="213" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B213" s="23"/>
     </row>
-    <row r="214" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B214" s="23"/>
       <c r="C214"/>
     </row>
-    <row r="215" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B215" s="23"/>
     </row>
-    <row r="216" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B216" s="23"/>
     </row>
-    <row r="217" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B217" s="23"/>
     </row>
-    <row r="218" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B218" s="23"/>
     </row>
-    <row r="219" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B219" s="23"/>
     </row>
-    <row r="220" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B220" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="246">
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="F172:F173"/>
-    <mergeCell ref="G172:G173"/>
-    <mergeCell ref="B172:B173"/>
-    <mergeCell ref="A174:A176"/>
-    <mergeCell ref="B174:B176"/>
-    <mergeCell ref="F174:F176"/>
-    <mergeCell ref="G174:G176"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="F168:F169"/>
-    <mergeCell ref="G168:G169"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="F170:F171"/>
-    <mergeCell ref="G170:G171"/>
-    <mergeCell ref="A163:A164"/>
-    <mergeCell ref="B163:B164"/>
-    <mergeCell ref="F163:F164"/>
-    <mergeCell ref="G163:G164"/>
-    <mergeCell ref="A165:A167"/>
-    <mergeCell ref="B165:B167"/>
-    <mergeCell ref="F165:F167"/>
-    <mergeCell ref="G165:G167"/>
-    <mergeCell ref="A159:A160"/>
-    <mergeCell ref="B159:B160"/>
-    <mergeCell ref="F159:F160"/>
-    <mergeCell ref="G159:G160"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="B161:B162"/>
-    <mergeCell ref="F161:F162"/>
-    <mergeCell ref="G161:G162"/>
-    <mergeCell ref="A154:A156"/>
-    <mergeCell ref="B154:B156"/>
-    <mergeCell ref="F154:F156"/>
-    <mergeCell ref="G154:G156"/>
-    <mergeCell ref="A157:A158"/>
-    <mergeCell ref="B157:B158"/>
-    <mergeCell ref="F157:F158"/>
-    <mergeCell ref="G157:G158"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="F148:F149"/>
-    <mergeCell ref="G148:G149"/>
-    <mergeCell ref="A150:A151"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="F150:F151"/>
-    <mergeCell ref="G150:G151"/>
-    <mergeCell ref="A130:A132"/>
-    <mergeCell ref="B130:B132"/>
-    <mergeCell ref="F130:F132"/>
-    <mergeCell ref="G130:G132"/>
-    <mergeCell ref="A136:A138"/>
-    <mergeCell ref="B136:B138"/>
-    <mergeCell ref="F136:F138"/>
-    <mergeCell ref="G136:G138"/>
-    <mergeCell ref="A139:A141"/>
-    <mergeCell ref="B139:B141"/>
-    <mergeCell ref="F139:F141"/>
-    <mergeCell ref="G139:G141"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="F82:F83"/>
-    <mergeCell ref="G82:G83"/>
-    <mergeCell ref="A122:A124"/>
-    <mergeCell ref="B122:B124"/>
-    <mergeCell ref="F122:F124"/>
-    <mergeCell ref="G122:G124"/>
-    <mergeCell ref="A125:A127"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="F125:F127"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="F75:F76"/>
-    <mergeCell ref="G75:G76"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="F77:F78"/>
-    <mergeCell ref="G77:G78"/>
-    <mergeCell ref="A79:A81"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="F79:F81"/>
-    <mergeCell ref="G79:G81"/>
-    <mergeCell ref="F86:F87"/>
-    <mergeCell ref="G86:G87"/>
-    <mergeCell ref="B88:B90"/>
-    <mergeCell ref="A88:A90"/>
-    <mergeCell ref="F88:F90"/>
-    <mergeCell ref="G88:G90"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="F84:F85"/>
-    <mergeCell ref="G84:G85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="A145:A147"/>
+    <mergeCell ref="B145:B147"/>
+    <mergeCell ref="F145:F147"/>
+    <mergeCell ref="G145:G147"/>
+    <mergeCell ref="A152:A153"/>
+    <mergeCell ref="B152:B153"/>
+    <mergeCell ref="F152:F153"/>
+    <mergeCell ref="G152:G153"/>
+    <mergeCell ref="A133:A135"/>
+    <mergeCell ref="B133:B135"/>
+    <mergeCell ref="F133:F135"/>
+    <mergeCell ref="G133:G135"/>
+    <mergeCell ref="G125:G127"/>
+    <mergeCell ref="A142:A144"/>
+    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="F142:F144"/>
+    <mergeCell ref="G142:G144"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="F128:F129"/>
+    <mergeCell ref="G128:G129"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="F107:F109"/>
+    <mergeCell ref="G107:G109"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="F110:F111"/>
+    <mergeCell ref="G110:G111"/>
+    <mergeCell ref="B119:B121"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="A115:A116"/>
+    <mergeCell ref="B115:B116"/>
+    <mergeCell ref="F115:F116"/>
+    <mergeCell ref="G115:G116"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="B117:B118"/>
+    <mergeCell ref="F117:F118"/>
+    <mergeCell ref="G117:G118"/>
+    <mergeCell ref="A112:A114"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="F112:F114"/>
+    <mergeCell ref="G112:G114"/>
+    <mergeCell ref="F119:F121"/>
+    <mergeCell ref="G119:G121"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="F100:F101"/>
+    <mergeCell ref="G100:G101"/>
+    <mergeCell ref="A102:A104"/>
+    <mergeCell ref="B102:B104"/>
+    <mergeCell ref="F102:F104"/>
+    <mergeCell ref="G102:G104"/>
+    <mergeCell ref="A105:A106"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="F105:F106"/>
+    <mergeCell ref="G105:G106"/>
+    <mergeCell ref="B93:B95"/>
+    <mergeCell ref="F93:F95"/>
+    <mergeCell ref="G93:G95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="F96:F97"/>
+    <mergeCell ref="G96:G97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="F98:F99"/>
+    <mergeCell ref="G98:G99"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="F57:F59"/>
+    <mergeCell ref="G57:G59"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="B60:B63"/>
+    <mergeCell ref="F60:F63"/>
+    <mergeCell ref="G60:G63"/>
+    <mergeCell ref="G91:G92"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="F91:F92"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="B68:B71"/>
+    <mergeCell ref="F68:F71"/>
+    <mergeCell ref="G68:G71"/>
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="B64:B67"/>
+    <mergeCell ref="F64:F67"/>
+    <mergeCell ref="G64:G67"/>
+    <mergeCell ref="A72:A74"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="F72:F74"/>
+    <mergeCell ref="G72:G74"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="F48:F50"/>
+    <mergeCell ref="G48:G50"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="F51:F53"/>
+    <mergeCell ref="G51:G53"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="F54:F56"/>
+    <mergeCell ref="G54:G56"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="F37:F40"/>
+    <mergeCell ref="G37:G40"/>
+    <mergeCell ref="A41:A44"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="F41:F44"/>
+    <mergeCell ref="G41:G44"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="F45:F47"/>
+    <mergeCell ref="G45:G47"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="G22:G25"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="G26:G29"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="F22:F25"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A9:A11"/>
@@ -3078,134 +3128,102 @@
     <mergeCell ref="G33:G36"/>
     <mergeCell ref="A30:A32"/>
     <mergeCell ref="B30:B32"/>
-    <mergeCell ref="F30:F32"/>
-    <mergeCell ref="G30:G32"/>
-    <mergeCell ref="G22:G25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="F26:F29"/>
-    <mergeCell ref="G26:G29"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="F22:F25"/>
-    <mergeCell ref="A37:A40"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="F37:F40"/>
-    <mergeCell ref="G37:G40"/>
-    <mergeCell ref="A41:A44"/>
-    <mergeCell ref="B41:B44"/>
-    <mergeCell ref="F41:F44"/>
-    <mergeCell ref="G41:G44"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="B45:B47"/>
-    <mergeCell ref="F45:F47"/>
-    <mergeCell ref="G45:G47"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="F48:F50"/>
-    <mergeCell ref="G48:G50"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="B51:B53"/>
-    <mergeCell ref="F51:F53"/>
-    <mergeCell ref="G51:G53"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="B54:B56"/>
-    <mergeCell ref="F54:F56"/>
-    <mergeCell ref="G54:G56"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="F57:F59"/>
-    <mergeCell ref="G57:G59"/>
-    <mergeCell ref="A60:A63"/>
-    <mergeCell ref="B60:B63"/>
-    <mergeCell ref="F60:F63"/>
-    <mergeCell ref="G60:G63"/>
-    <mergeCell ref="G91:G92"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="F91:F92"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="B68:B71"/>
-    <mergeCell ref="F68:F71"/>
-    <mergeCell ref="G68:G71"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="B64:B67"/>
-    <mergeCell ref="F64:F67"/>
-    <mergeCell ref="G64:G67"/>
-    <mergeCell ref="A72:A74"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="F72:F74"/>
-    <mergeCell ref="G72:G74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="F75:F76"/>
+    <mergeCell ref="G75:G76"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="F77:F78"/>
+    <mergeCell ref="G77:G78"/>
+    <mergeCell ref="A79:A81"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="F79:F81"/>
+    <mergeCell ref="G79:G81"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="F82:F83"/>
+    <mergeCell ref="G82:G83"/>
+    <mergeCell ref="A122:A124"/>
+    <mergeCell ref="B122:B124"/>
+    <mergeCell ref="F122:F124"/>
+    <mergeCell ref="G122:G124"/>
+    <mergeCell ref="A125:A127"/>
+    <mergeCell ref="B125:B127"/>
+    <mergeCell ref="F125:F127"/>
+    <mergeCell ref="F86:F87"/>
+    <mergeCell ref="G86:G87"/>
+    <mergeCell ref="B88:B90"/>
+    <mergeCell ref="A88:A90"/>
+    <mergeCell ref="F88:F90"/>
+    <mergeCell ref="G88:G90"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="F84:F85"/>
+    <mergeCell ref="G84:G85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
     <mergeCell ref="A93:A95"/>
-    <mergeCell ref="B93:B95"/>
-    <mergeCell ref="F93:F95"/>
-    <mergeCell ref="G93:G95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="F96:F97"/>
-    <mergeCell ref="G96:G97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="F98:F99"/>
-    <mergeCell ref="G98:G99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="F100:F101"/>
-    <mergeCell ref="G100:G101"/>
-    <mergeCell ref="A102:A104"/>
-    <mergeCell ref="B102:B104"/>
-    <mergeCell ref="F102:F104"/>
-    <mergeCell ref="G102:G104"/>
-    <mergeCell ref="A105:A106"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="F105:F106"/>
-    <mergeCell ref="G105:G106"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="F107:F109"/>
-    <mergeCell ref="G107:G109"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="B110:B111"/>
-    <mergeCell ref="F110:F111"/>
-    <mergeCell ref="G110:G111"/>
-    <mergeCell ref="B119:B121"/>
-    <mergeCell ref="A119:A121"/>
-    <mergeCell ref="A115:A116"/>
-    <mergeCell ref="B115:B116"/>
-    <mergeCell ref="F115:F116"/>
-    <mergeCell ref="G115:G116"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="B117:B118"/>
-    <mergeCell ref="F117:F118"/>
-    <mergeCell ref="G117:G118"/>
-    <mergeCell ref="A112:A114"/>
-    <mergeCell ref="B112:B114"/>
-    <mergeCell ref="F112:F114"/>
-    <mergeCell ref="G112:G114"/>
+    <mergeCell ref="A130:A132"/>
+    <mergeCell ref="B130:B132"/>
+    <mergeCell ref="F130:F132"/>
+    <mergeCell ref="G130:G132"/>
+    <mergeCell ref="A136:A138"/>
+    <mergeCell ref="B136:B138"/>
+    <mergeCell ref="F136:F138"/>
+    <mergeCell ref="G136:G138"/>
+    <mergeCell ref="A139:A141"/>
+    <mergeCell ref="B139:B141"/>
+    <mergeCell ref="F139:F141"/>
+    <mergeCell ref="G139:G141"/>
+    <mergeCell ref="A154:A156"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="F154:F156"/>
+    <mergeCell ref="G154:G156"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="F157:F158"/>
+    <mergeCell ref="G157:G158"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="F148:F149"/>
+    <mergeCell ref="G148:G149"/>
+    <mergeCell ref="A150:A151"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="F150:F151"/>
+    <mergeCell ref="G150:G151"/>
+    <mergeCell ref="A163:A164"/>
+    <mergeCell ref="B163:B164"/>
+    <mergeCell ref="F163:F164"/>
+    <mergeCell ref="G163:G164"/>
+    <mergeCell ref="A165:A167"/>
+    <mergeCell ref="B165:B167"/>
+    <mergeCell ref="F165:F167"/>
+    <mergeCell ref="G165:G167"/>
+    <mergeCell ref="A159:A160"/>
+    <mergeCell ref="B159:B160"/>
+    <mergeCell ref="F159:F160"/>
+    <mergeCell ref="G159:G160"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="F161:F162"/>
+    <mergeCell ref="G161:G162"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="F172:F173"/>
+    <mergeCell ref="G172:G173"/>
+    <mergeCell ref="B172:B173"/>
+    <mergeCell ref="A174:A176"/>
+    <mergeCell ref="B174:B176"/>
+    <mergeCell ref="F174:F176"/>
+    <mergeCell ref="G174:G176"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="F168:F169"/>
+    <mergeCell ref="G168:G169"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="F170:F171"/>
+    <mergeCell ref="G170:G171"/>
     <mergeCell ref="B168:B169"/>
-    <mergeCell ref="F119:F121"/>
-    <mergeCell ref="G119:G121"/>
-    <mergeCell ref="G125:G127"/>
-    <mergeCell ref="A142:A144"/>
-    <mergeCell ref="B142:B144"/>
-    <mergeCell ref="F142:F144"/>
-    <mergeCell ref="G142:G144"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="F128:F129"/>
-    <mergeCell ref="G128:G129"/>
-    <mergeCell ref="A145:A147"/>
-    <mergeCell ref="B145:B147"/>
-    <mergeCell ref="F145:F147"/>
-    <mergeCell ref="G145:G147"/>
-    <mergeCell ref="A152:A153"/>
-    <mergeCell ref="B152:B153"/>
-    <mergeCell ref="F152:F153"/>
-    <mergeCell ref="G152:G153"/>
-    <mergeCell ref="A133:A135"/>
-    <mergeCell ref="B133:B135"/>
-    <mergeCell ref="F133:F135"/>
-    <mergeCell ref="G133:G135"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
